--- a/artfynd/A 21284-2026 artfynd.xlsx
+++ b/artfynd/A 21284-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131902048</v>
+        <v>131900323</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>463710</v>
+        <v>464130</v>
       </c>
       <c r="R2" t="n">
-        <v>6788923</v>
+        <v>6788932</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,17 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131902624</v>
+        <v>131900297</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>463597</v>
+        <v>464132</v>
       </c>
       <c r="R3" t="n">
-        <v>6788860</v>
+        <v>6788922</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,17 +862,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131902053</v>
+        <v>131900410</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>463710</v>
+        <v>464141</v>
       </c>
       <c r="R4" t="n">
-        <v>6788923</v>
+        <v>6788971</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,17 +959,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131902512</v>
+        <v>131902508</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131902164</v>
+        <v>131902908</v>
       </c>
       <c r="B6" t="n">
-        <v>79085</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>463693</v>
+        <v>463699</v>
       </c>
       <c r="R6" t="n">
-        <v>6788840</v>
+        <v>6788977</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131902908</v>
+        <v>131901653</v>
       </c>
       <c r="B7" t="n">
-        <v>78993</v>
+        <v>91937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>463699</v>
+        <v>463892</v>
       </c>
       <c r="R7" t="n">
-        <v>6788977</v>
+        <v>6789126</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,57 +1250,52 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131899382</v>
+        <v>131899185</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>464087</v>
+        <v>464113</v>
       </c>
       <c r="R8" t="n">
-        <v>6788862</v>
+        <v>6788858</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,14 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131902296</v>
+        <v>131899801</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1390,14 +1385,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>463633</v>
+        <v>464098</v>
       </c>
       <c r="R9" t="n">
-        <v>6788814</v>
+        <v>6788894</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1432,11 +1427,6 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1454,57 +1444,52 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131901760</v>
+        <v>131900207</v>
       </c>
       <c r="B10" t="n">
-        <v>57950</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>463848</v>
+        <v>464122</v>
       </c>
       <c r="R10" t="n">
-        <v>6789114</v>
+        <v>6788896</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,52 +1541,52 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131902508</v>
+        <v>131900329</v>
       </c>
       <c r="B11" t="n">
-        <v>78993</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>463582</v>
+        <v>464130</v>
       </c>
       <c r="R11" t="n">
-        <v>6788856</v>
+        <v>6788932</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,52 +1638,52 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131902263</v>
+        <v>131900379</v>
       </c>
       <c r="B12" t="n">
-        <v>79917</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>463633</v>
+        <v>464130</v>
       </c>
       <c r="R12" t="n">
-        <v>6788814</v>
+        <v>6788950</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,21 +1735,21 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131902169</v>
+        <v>131900413</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1788,14 +1773,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>463693</v>
+        <v>464141</v>
       </c>
       <c r="R13" t="n">
-        <v>6788840</v>
+        <v>6788971</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,21 +1832,21 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131902458</v>
+        <v>131901655</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1889,13 +1874,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>463561</v>
+        <v>463892</v>
       </c>
       <c r="R14" t="n">
-        <v>6788842</v>
+        <v>6789126</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1925,11 +1910,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1949,57 +1929,52 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131901996</v>
+        <v>131901762</v>
       </c>
       <c r="B15" t="n">
-        <v>57141</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>463740</v>
+        <v>463848</v>
       </c>
       <c r="R15" t="n">
-        <v>6788944</v>
+        <v>6789114</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,57 +2033,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131902617</v>
+        <v>131901872</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>463597</v>
+        <v>463779</v>
       </c>
       <c r="R16" t="n">
-        <v>6788860</v>
+        <v>6789025</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2142,7 +2108,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På tre torrtallar</t>
+          <t>Sparsamt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2169,14 +2135,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131902911</v>
+        <v>131901955</v>
       </c>
       <c r="B17" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2204,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463699</v>
+        <v>463761</v>
       </c>
       <c r="R17" t="n">
-        <v>6788977</v>
+        <v>6789030</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2269,11 +2235,11 @@
         <v>131901998</v>
       </c>
       <c r="B18" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2363,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131902049</v>
+        <v>131902053</v>
       </c>
       <c r="B19" t="n">
-        <v>79085</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2460,50 +2426,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131899796</v>
+        <v>131902169</v>
       </c>
       <c r="B20" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>464098</v>
+        <v>463693</v>
       </c>
       <c r="R20" t="n">
-        <v>6788894</v>
+        <v>6788840</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2555,57 +2516,52 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131899308</v>
+        <v>131902296</v>
       </c>
       <c r="B21" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>464087</v>
+        <v>463633</v>
       </c>
       <c r="R21" t="n">
-        <v>6788862</v>
+        <v>6788814</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2640,6 +2596,11 @@
           <t>2026-03-24</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2657,21 +2618,21 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131899801</v>
+        <v>131902458</v>
       </c>
       <c r="B22" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2695,17 +2656,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gutkrok, Dlr</t>
+          <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>464098</v>
+        <v>463561</v>
       </c>
       <c r="R22" t="n">
-        <v>6788894</v>
+        <v>6788842</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2735,6 +2696,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Måttligt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2754,57 +2720,52 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum, Håkan Thenander</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131901744</v>
+        <v>131902512</v>
       </c>
       <c r="B23" t="n">
-        <v>8455</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fännsjöberget, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>463848</v>
+        <v>463582</v>
       </c>
       <c r="R23" t="n">
-        <v>6789114</v>
+        <v>6788856</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2863,14 +2824,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131901955</v>
+        <v>131902624</v>
       </c>
       <c r="B24" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2898,10 +2859,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>463761</v>
+        <v>463597</v>
       </c>
       <c r="R24" t="n">
-        <v>6789030</v>
+        <v>6788860</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2963,11 +2924,11 @@
         <v>131902815</v>
       </c>
       <c r="B25" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3062,32 +3023,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131902904</v>
+        <v>131902911</v>
       </c>
       <c r="B26" t="n">
-        <v>97987</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3159,14 +3120,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131901872</v>
+        <v>131902988</v>
       </c>
       <c r="B27" t="n">
-        <v>79327</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3194,13 +3155,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>463779</v>
+        <v>463793</v>
       </c>
       <c r="R27" t="n">
-        <v>6789025</v>
+        <v>6789072</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3230,11 +3191,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Sparsamt i en radie av ca 50 meter, synfältet</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3264,7 +3220,7 @@
         <v>131902839</v>
       </c>
       <c r="B28" t="n">
-        <v>79351</v>
+        <v>79397</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3358,10 +3314,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131901762</v>
+        <v>131900374</v>
       </c>
       <c r="B29" t="n">
-        <v>79327</v>
+        <v>79130</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3369,34 +3325,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fännsjöberget, Dlr</t>
+          <t>Gutkrok, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>463848</v>
+        <v>464130</v>
       </c>
       <c r="R29" t="n">
-        <v>6789114</v>
+        <v>6788950</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3448,10 +3404,1616 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131902048</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fännsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>463710</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6788923</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131900290</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gutkrok, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>464132</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6788922</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131899382</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gutkrok, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>464087</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6788862</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131900191</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gutkrok, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>464122</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6788896</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131901760</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Fännsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>463848</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6789114</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131899308</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gutkrok, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>464087</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6788862</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131899796</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gutkrok, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>464098</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6788894</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131902984</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fännsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>463793</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6789072</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131901996</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fännsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>463740</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6788944</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131900199</v>
+      </c>
+      <c r="B39" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Gutkrok, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>464122</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6788896</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131901744</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Fännsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>463848</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6789114</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131902617</v>
+      </c>
+      <c r="B41" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fännsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>463597</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6788860</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På tre torrtallar</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131902904</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Fännsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>463699</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6788977</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131902049</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Fännsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>463710</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6788923</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131902164</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Fännsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>463693</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6788840</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131902263</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fännsjöberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>463633</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6788814</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21284-2026 artfynd.xlsx
+++ b/artfynd/A 21284-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900323</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900297</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900410</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902508</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902908</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131901653</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131899185</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131899801</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900207</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900329</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900379</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900413</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131901655</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131901762</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131901872</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131901955</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131901998</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902053</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902169</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2622,6 +2722,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902296</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2724,6 +2829,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902458</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2821,6 +2931,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902512</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2918,6 +3033,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902624</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3020,6 +3140,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902815</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3117,6 +3242,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902911</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3214,6 +3344,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902988</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3311,6 +3446,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902839</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3408,6 +3548,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900374</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3505,6 +3650,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902048</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3602,6 +3752,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900290</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3704,6 +3859,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131899382</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3806,6 +3966,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900191</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3908,6 +4073,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131901760</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4010,6 +4180,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131899308</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4112,6 +4287,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131899796</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4214,6 +4394,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902984</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4316,6 +4501,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131901996</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4413,6 +4603,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131900199</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4515,6 +4710,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131901744</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4626,6 +4826,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902617</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4723,6 +4928,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902904</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4820,6 +5030,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902049</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4917,6 +5132,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902164</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5014,8 +5234,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131902263</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>